--- a/specs/spec3.xlsx
+++ b/specs/spec3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SnigdhaYS\Documents\LTSpice_LDO_Automation\specs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE0F6230-58A4-4E8E-B548-724102914E6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2433C49-E1FE-41F8-B9C1-A8FCEBEBF851}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -755,7 +755,7 @@
         <v>13</v>
       </c>
       <c r="B13">
-        <v>120</v>
+        <v>500</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="26" x14ac:dyDescent="0.6">
